--- a/zaini_case_audit_output/outputs/excel/08_case_analysis.xlsx
+++ b/zaini_case_audit_output/outputs/excel/08_case_analysis.xlsx
@@ -69787,14 +69787,14 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
+          <t>اتفاقية الصلح والتخارج في شركات أحمد زيني وأولاده ـ مصدقة من المحكمة | مرفقات المدعي عدنان زيني في الدعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -71516,7 +71516,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -71524,7 +71524,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx | صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf | صك حكم نهائي ـ الاستئناف الثانية ـ نسخة | ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf | مذكرة طلب النقض على الحكم النهائي</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx | صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf | صك حكم نهائي ـ الاستئناف الثانية ـ نسخة | طلب النقض على صك الاستئناف الثانية | مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -71551,7 +71551,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>76</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -71559,7 +71559,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>الشكوى ومرفقاتها | حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447 | حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf | شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf | شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
+          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx | صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf | صك حكم نهائي ـ الاستئناف الثانية ـ نسخة | ضبط جلسة رقم 34 يوم 12-02-1445 هـ للقضية رقم 42824717 .pdf | مذكرة طلب النقض على الحكم النهائي</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -71586,15 +71586,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>التماس الشيخ أسامه زيني ـ القضية 42824717 ـ من المستشار.docx | صك حكم نهائي ضد الشيخ اسامة زيني ـ دعوى 42824717 - 13-03-1445 هـ.pdf | صك حكم نهائي ـ الاستئناف الثانية ـ نسخة | طلب النقض على صك الاستئناف الثانية | مذكرة طلب النقض على الحكم النهائي</t>
+          <t>الشكوى ومرفقاتها | حكم نهائي بإبراء ذمة الشيخ من تنفيذ عاتقة ـ 13-04-1447 | حكم نهائي بنقض حكم ابراء ذمة الشيخ أسامة من طلب تنفيذ الوالدة عاتقة الحرازي - 22-07-1447 ـ 4771864931.pdf | شكوى أسامة أحمد زيني ـ دعوى رقم 42824717 ـ 30-04-1445 ـ حجم اقل.pdf | شكوى أسامة أحمد زيني ـ دعوى رقم 42824717.pdf</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
